--- a/test_results_dashboard.xlsx
+++ b/test_results_dashboard.xlsx
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>51.86</v>
+        <v>74.03</v>
       </c>
     </row>
     <row r="3">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>55.48</v>
+        <v>134.77</v>
       </c>
     </row>
     <row r="4">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>171</v>
+        <v>178.78</v>
       </c>
     </row>
     <row r="5">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>70.62</v>
+        <v>113.89</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>163.57</v>
+        <v>106.65</v>
       </c>
     </row>
     <row r="7">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>112.79</v>
+        <v>179.06</v>
       </c>
     </row>
     <row r="8">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>167.52</v>
+        <v>94.86</v>
       </c>
     </row>
     <row r="9">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>142.75</v>
+        <v>106.24</v>
       </c>
     </row>
     <row r="10">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>125.29</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="11">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>58.49</v>
+        <v>113.38</v>
       </c>
     </row>
     <row r="12">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>162.62</v>
+        <v>167.94</v>
       </c>
     </row>
     <row r="13">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>163.36</v>
+        <v>148.97</v>
       </c>
     </row>
     <row r="14">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>100.41</v>
+        <v>67.55</v>
       </c>
     </row>
     <row r="15">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>118.21</v>
+        <v>89.68000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>77.75</v>
+        <v>147.86</v>
       </c>
     </row>
     <row r="17">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>53.21</v>
+        <v>107.25</v>
       </c>
     </row>
     <row r="18">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>144.58</v>
+        <v>76.59</v>
       </c>
     </row>
     <row r="19">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>53.11</v>
+        <v>72.59</v>
       </c>
     </row>
     <row r="20">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>63.64</v>
+        <v>124.53</v>
       </c>
     </row>
     <row r="21">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>54.86</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="22">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>115.12</v>
+        <v>55.39</v>
       </c>
     </row>
     <row r="23">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>119.17</v>
+        <v>69.91</v>
       </c>
     </row>
     <row r="24">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>125.57</v>
+        <v>100.66</v>
       </c>
     </row>
     <row r="25">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>109.55</v>
+        <v>112.54</v>
       </c>
     </row>
     <row r="26">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>97.12</v>
+        <v>150.84</v>
       </c>
     </row>
     <row r="27">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>54.67</v>
+        <v>111.86</v>
       </c>
     </row>
     <row r="28">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>164.21</v>
+        <v>120.43</v>
       </c>
     </row>
     <row r="29">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>84.05</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>146.63</v>
+        <v>123.54</v>
       </c>
     </row>
     <row r="31">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>49.26</v>
+        <v>174.14</v>
       </c>
     </row>
     <row r="32">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>61.85</v>
+        <v>102.77</v>
       </c>
     </row>
     <row r="33">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>149.18</v>
+        <v>127.43</v>
       </c>
     </row>
     <row r="34">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>141.22</v>
+        <v>80.97</v>
       </c>
     </row>
     <row r="35">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>147.32</v>
+        <v>72.05</v>
       </c>
     </row>
     <row r="36">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>158.84</v>
+        <v>116.93</v>
       </c>
     </row>
     <row r="37">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>101.94</v>
+        <v>127.06</v>
       </c>
     </row>
     <row r="38">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>111.92</v>
+        <v>153.09</v>
       </c>
     </row>
     <row r="39">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>152.08</v>
+        <v>174.69</v>
       </c>
     </row>
     <row r="40">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>116.44</v>
+        <v>123.45</v>
       </c>
     </row>
     <row r="41">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>138.3</v>
+        <v>93.70999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>51.76</v>
+        <v>158.8</v>
       </c>
     </row>
     <row r="43">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>172.81</v>
+        <v>113.33</v>
       </c>
     </row>
     <row r="44">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>65.94</v>
+        <v>67.55</v>
       </c>
     </row>
     <row r="45">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>87.48</v>
+        <v>128.68</v>
       </c>
     </row>
     <row r="46">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>77</v>
+        <v>130.05</v>
       </c>
     </row>
     <row r="47">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>83.5</v>
+        <v>136.35</v>
       </c>
     </row>
     <row r="48">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>133.06</v>
+        <v>97.51000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>99.61</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="50">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>153.73</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="51">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>80.93000000000001</v>
+        <v>130.08</v>
       </c>
     </row>
     <row r="52">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>56.68</v>
+        <v>166.58</v>
       </c>
     </row>
     <row r="53">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>163.34</v>
+        <v>94.45</v>
       </c>
     </row>
     <row r="54">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>67.76000000000001</v>
+        <v>90.48</v>
       </c>
     </row>
     <row r="55">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>132.2</v>
+        <v>115.39</v>
       </c>
     </row>
     <row r="56">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>104.18</v>
+        <v>140.85</v>
       </c>
     </row>
     <row r="57">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>74.90000000000001</v>
+        <v>162.83</v>
       </c>
     </row>
     <row r="58">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>62.34</v>
+        <v>93.36</v>
       </c>
     </row>
     <row r="59">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>167.88</v>
+        <v>161.53</v>
       </c>
     </row>
     <row r="60">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>162.9</v>
+        <v>154.98</v>
       </c>
     </row>
     <row r="61">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>45.31</v>
+        <v>108.64</v>
       </c>
     </row>
     <row r="62">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>46.87</v>
+        <v>104.71</v>
       </c>
     </row>
     <row r="63">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>75.02</v>
+        <v>173.55</v>
       </c>
     </row>
     <row r="64">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>97.66</v>
+        <v>144.4</v>
       </c>
     </row>
     <row r="65">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>158.64</v>
+        <v>62.46</v>
       </c>
     </row>
     <row r="66">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>51.83</v>
+        <v>171.63</v>
       </c>
     </row>
     <row r="67">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>156.43</v>
+        <v>111.97</v>
       </c>
     </row>
     <row r="68">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>62.21</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="69">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>112.73</v>
+        <v>57.42</v>
       </c>
     </row>
     <row r="70">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>173.48</v>
+        <v>125.11</v>
       </c>
     </row>
     <row r="71">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>145.72</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="72">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>179.17</v>
+        <v>120.21</v>
       </c>
     </row>
     <row r="73">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>59.93</v>
+        <v>77.48</v>
       </c>
     </row>
     <row r="74">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>100.83</v>
+        <v>156.8</v>
       </c>
     </row>
     <row r="75">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>97.25</v>
+        <v>155.9</v>
       </c>
     </row>
     <row r="76">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>80.89</v>
+        <v>128.72</v>
       </c>
     </row>
     <row r="77">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>52.54</v>
+        <v>132.48</v>
       </c>
     </row>
     <row r="78">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>61.22</v>
+        <v>150.39</v>
       </c>
     </row>
     <row r="79">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>172.25</v>
+        <v>131.6</v>
       </c>
     </row>
     <row r="80">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>173.22</v>
+        <v>88.08</v>
       </c>
     </row>
     <row r="81">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>68.81</v>
+        <v>62.46</v>
       </c>
     </row>
     <row r="82">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>141.92</v>
+        <v>129.53</v>
       </c>
     </row>
     <row r="83">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>73.64</v>
+        <v>140.91</v>
       </c>
     </row>
     <row r="84">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>164.3</v>
+        <v>149.74</v>
       </c>
     </row>
     <row r="85">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>60.24</v>
+        <v>122.56</v>
       </c>
     </row>
     <row r="86">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>171.55</v>
+        <v>154.09</v>
       </c>
     </row>
     <row r="87">
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>161.83</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="88">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>47.5</v>
+        <v>92.36</v>
       </c>
     </row>
     <row r="89">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>172.76</v>
+        <v>115.9</v>
       </c>
     </row>
     <row r="90">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>162.26</v>
+        <v>83.48</v>
       </c>
     </row>
     <row r="91">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>58.13</v>
+        <v>75.45</v>
       </c>
     </row>
     <row r="92">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>70.19</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="93">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>77.68000000000001</v>
+        <v>95.34999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>83.78</v>
+        <v>175.31</v>
       </c>
     </row>
     <row r="95">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>137.94</v>
+        <v>163.82</v>
       </c>
     </row>
     <row r="96">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>98.45999999999999</v>
+        <v>129.93</v>
       </c>
     </row>
     <row r="97">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>179.08</v>
+        <v>59.12</v>
       </c>
     </row>
     <row r="98">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>118.35</v>
+        <v>145.8</v>
       </c>
     </row>
     <row r="99">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>143.08</v>
+        <v>86.16</v>
       </c>
     </row>
     <row r="100">
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>140.55</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="101">
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>165.32</v>
+        <v>73.27</v>
       </c>
     </row>
     <row r="102">
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>100.27</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="103">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>108.25</v>
+        <v>168.61</v>
       </c>
     </row>
     <row r="104">
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>124.51</v>
+        <v>108.96</v>
       </c>
     </row>
     <row r="105">
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>72.91</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="106">
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>170.18</v>
+        <v>120.88</v>
       </c>
     </row>
     <row r="107">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>123.75</v>
+        <v>83.08</v>
       </c>
     </row>
     <row r="108">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>128.22</v>
+        <v>102.87</v>
       </c>
     </row>
     <row r="109">
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>131.17</v>
+        <v>144.07</v>
       </c>
     </row>
     <row r="110">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>138.26</v>
+        <v>67.62</v>
       </c>
     </row>
     <row r="111">
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>146.85</v>
+        <v>178.94</v>
       </c>
     </row>
     <row r="112">
@@ -3936,7 +3936,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>54.91</v>
+        <v>97.81999999999999</v>
       </c>
     </row>
     <row r="113">
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>83.39</v>
+        <v>146.39</v>
       </c>
     </row>
     <row r="114">
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>54.64</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="115">
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>51.35</v>
+        <v>130.68</v>
       </c>
     </row>
     <row r="116">
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>122.63</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="117">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>158.1</v>
+        <v>65.98</v>
       </c>
     </row>
     <row r="118">
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>57.24</v>
+        <v>95.81999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>118.17</v>
+        <v>97.81999999999999</v>
       </c>
     </row>
     <row r="120">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>57.49</v>
+        <v>111.68</v>
       </c>
     </row>
     <row r="121">
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>139.77</v>
+        <v>108.49</v>
       </c>
     </row>
     <row r="122">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>52.9</v>
+        <v>115.81</v>
       </c>
     </row>
     <row r="123">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>142.49</v>
+        <v>135.82</v>
       </c>
     </row>
     <row r="124">
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>100.6</v>
+        <v>126.53</v>
       </c>
     </row>
     <row r="125">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>49.58</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>112.69</v>
+        <v>123.41</v>
       </c>
     </row>
     <row r="127">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>162.47</v>
+        <v>113.57</v>
       </c>
     </row>
     <row r="128">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>93.56</v>
+        <v>67.05</v>
       </c>
     </row>
     <row r="129">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>87.13</v>
+        <v>56.06</v>
       </c>
     </row>
     <row r="130">
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>45.71</v>
+        <v>154.21</v>
       </c>
     </row>
     <row r="131">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>118.77</v>
+        <v>122.28</v>
       </c>
     </row>
     <row r="132">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>153.97</v>
+        <v>59.59</v>
       </c>
     </row>
     <row r="133">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>143.79</v>
+        <v>171.44</v>
       </c>
     </row>
     <row r="134">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>130.31</v>
+        <v>110.58</v>
       </c>
     </row>
     <row r="135">
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>70.09999999999999</v>
+        <v>150.34</v>
       </c>
     </row>
     <row r="136">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>47.59</v>
+        <v>62.02</v>
       </c>
     </row>
     <row r="137">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>154.54</v>
+        <v>82.44</v>
       </c>
     </row>
     <row r="138">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>109.37</v>
+        <v>151.19</v>
       </c>
     </row>
     <row r="139">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>114.66</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="140">
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>98.19</v>
+        <v>146.54</v>
       </c>
     </row>
     <row r="141">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>161.78</v>
+        <v>66.73</v>
       </c>
     </row>
     <row r="142">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>114.2</v>
+        <v>148.26</v>
       </c>
     </row>
     <row r="143">
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>178.13</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="144">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>72.02</v>
+        <v>148.86</v>
       </c>
     </row>
     <row r="145">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>47.86</v>
+        <v>130.51</v>
       </c>
     </row>
     <row r="146">
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>133.81</v>
+        <v>145.7</v>
       </c>
     </row>
     <row r="147">
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>59.96</v>
+        <v>159.42</v>
       </c>
     </row>
     <row r="148">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>105.7</v>
+        <v>119.56</v>
       </c>
     </row>
     <row r="149">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>131.54</v>
+        <v>128.36</v>
       </c>
     </row>
     <row r="150">
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>159.46</v>
+        <v>120.85</v>
       </c>
     </row>
     <row r="151">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>58.3</v>
+        <v>113.89</v>
       </c>
     </row>
     <row r="152">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>123.7</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="153">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>49.79</v>
+        <v>139.64</v>
       </c>
     </row>
     <row r="154">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>107.19</v>
+        <v>141.87</v>
       </c>
     </row>
     <row r="155">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>98.29000000000001</v>
+        <v>95.89</v>
       </c>
     </row>
     <row r="156">
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>151.94</v>
+        <v>89.76000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>165.82</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="158">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>85.45999999999999</v>
+        <v>108.95</v>
       </c>
     </row>
     <row r="159">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>124.9</v>
+        <v>168.11</v>
       </c>
     </row>
     <row r="160">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>147.45</v>
+        <v>115.76</v>
       </c>
     </row>
     <row r="161">
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>138.65</v>
+        <v>67.81</v>
       </c>
     </row>
     <row r="162">
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>70.16</v>
+        <v>79.01000000000001</v>
       </c>
     </row>
     <row r="163">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>75.87</v>
+        <v>124.64</v>
       </c>
     </row>
     <row r="164">
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>117.58</v>
+        <v>165.68</v>
       </c>
     </row>
     <row r="165">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>138.76</v>
+        <v>142.39</v>
       </c>
     </row>
     <row r="166">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>62.23</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="167">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>171.85</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="168">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>141.93</v>
+        <v>161.15</v>
       </c>
     </row>
     <row r="169">
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>126.71</v>
+        <v>103.64</v>
       </c>
     </row>
     <row r="170">
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>115.2</v>
+        <v>158.94</v>
       </c>
     </row>
     <row r="171">
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>150.76</v>
+        <v>97.45999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>82.75</v>
+        <v>175.95</v>
       </c>
     </row>
     <row r="173">
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>99.55</v>
+        <v>100.05</v>
       </c>
     </row>
     <row r="174">
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>58.25</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="175">
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>109.56</v>
+        <v>80.15000000000001</v>
       </c>
     </row>
     <row r="176">
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>77.15000000000001</v>
+        <v>153.83</v>
       </c>
     </row>
     <row r="177">
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>74.23</v>
+        <v>127.17</v>
       </c>
     </row>
     <row r="178">
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>139.28</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="179">
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>53.2</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="180">
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>94.98</v>
+        <v>104.05</v>
       </c>
     </row>
     <row r="181">
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>145.38</v>
+        <v>153.37</v>
       </c>
     </row>
     <row r="182">
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>163.63</v>
+        <v>128.17</v>
       </c>
     </row>
     <row r="183">
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>151.29</v>
+        <v>134.36</v>
       </c>
     </row>
     <row r="184">
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>97.36</v>
+        <v>73.05</v>
       </c>
     </row>
     <row r="185">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>141.14</v>
+        <v>178.43</v>
       </c>
     </row>
     <row r="186">
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>150.02</v>
+        <v>117.54</v>
       </c>
     </row>
     <row r="187">
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>72.91</v>
+        <v>154.61</v>
       </c>
     </row>
     <row r="188">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>84.02</v>
+        <v>175.82</v>
       </c>
     </row>
     <row r="189">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>138.1</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="190">
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>71.7</v>
+        <v>157.78</v>
       </c>
     </row>
     <row r="191">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>167.28</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="192">
@@ -6336,7 +6336,7 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>114.87</v>
+        <v>86.69</v>
       </c>
     </row>
     <row r="193">
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>47.46</v>
+        <v>158.71</v>
       </c>
     </row>
     <row r="194">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>48.65</v>
+        <v>82.56999999999999</v>
       </c>
     </row>
     <row r="195">
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>159.31</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="196">
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>83.53</v>
+        <v>150.42</v>
       </c>
     </row>
     <row r="197">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>139.68</v>
+        <v>101.37</v>
       </c>
     </row>
     <row r="198">
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>84.72</v>
+        <v>107.42</v>
       </c>
     </row>
     <row r="199">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>128.75</v>
+        <v>127.84</v>
       </c>
     </row>
     <row r="200">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>102.55</v>
+        <v>119.13</v>
       </c>
     </row>
     <row r="201">
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>69</v>
+        <v>154.1</v>
       </c>
     </row>
     <row r="202">
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>144.24</v>
+        <v>133.47</v>
       </c>
     </row>
     <row r="203">
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>177.94</v>
+        <v>178.69</v>
       </c>
     </row>
     <row r="204">
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>89.23</v>
+        <v>90.15000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>63.33</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="206">
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>101.21</v>
+        <v>103.82</v>
       </c>
     </row>
     <row r="207">
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>68.45</v>
+        <v>137.11</v>
       </c>
     </row>
     <row r="208">
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>98.47</v>
+        <v>88.28</v>
       </c>
     </row>
     <row r="209">
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>83.23999999999999</v>
+        <v>153.06</v>
       </c>
     </row>
     <row r="210">
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>51.76</v>
+        <v>178.51</v>
       </c>
     </row>
     <row r="211">
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>167.11</v>
+        <v>166.85</v>
       </c>
     </row>
     <row r="212">
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>171.53</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="213">
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>88.62</v>
+        <v>95.09</v>
       </c>
     </row>
     <row r="214">
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>156.42</v>
+        <v>109.36</v>
       </c>
     </row>
     <row r="215">
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>162.92</v>
+        <v>84.01000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>99.92</v>
+        <v>126.16</v>
       </c>
     </row>
     <row r="217">
@@ -7086,7 +7086,7 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>60.48</v>
+        <v>163.36</v>
       </c>
     </row>
     <row r="218">
@@ -7116,7 +7116,7 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>93.53</v>
+        <v>127.31</v>
       </c>
     </row>
     <row r="219">
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>95.83</v>
+        <v>62.51</v>
       </c>
     </row>
     <row r="220">
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>81.2</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="221">
@@ -7206,7 +7206,7 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>123.94</v>
+        <v>66.44</v>
       </c>
     </row>
     <row r="222">
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>148.81</v>
+        <v>125.64</v>
       </c>
     </row>
     <row r="223">
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>60.36</v>
+        <v>171.5</v>
       </c>
     </row>
     <row r="224">
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>156.75</v>
+        <v>147.59</v>
       </c>
     </row>
     <row r="225">
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>158.2</v>
+        <v>80.29000000000001</v>
       </c>
     </row>
     <row r="226">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>69.97</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="227">
@@ -7386,7 +7386,7 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>73.23</v>
+        <v>167.74</v>
       </c>
     </row>
     <row r="228">
@@ -7416,7 +7416,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>94.59</v>
+        <v>127.79</v>
       </c>
     </row>
     <row r="229">
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>58.29</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="230">
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>118.54</v>
+        <v>146.48</v>
       </c>
     </row>
     <row r="231">
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>100.19</v>
+        <v>127.23</v>
       </c>
     </row>
     <row r="232">
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>115.7</v>
+        <v>75.18000000000001</v>
       </c>
     </row>
     <row r="233">
@@ -7566,7 +7566,7 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>108.54</v>
+        <v>127.66</v>
       </c>
     </row>
     <row r="234">
@@ -7596,7 +7596,7 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>177.19</v>
+        <v>144.57</v>
       </c>
     </row>
     <row r="235">
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>101.16</v>
+        <v>144.41</v>
       </c>
     </row>
     <row r="236">
@@ -7656,7 +7656,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>98.05</v>
+        <v>135.29</v>
       </c>
     </row>
     <row r="237">
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>116.84</v>
+        <v>145.41</v>
       </c>
     </row>
     <row r="238">
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>49.2</v>
+        <v>122.99</v>
       </c>
     </row>
     <row r="239">
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>164.56</v>
+        <v>147.77</v>
       </c>
     </row>
     <row r="240">
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>59.77</v>
+        <v>96.72</v>
       </c>
     </row>
     <row r="241">
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>105.32</v>
+        <v>130.19</v>
       </c>
     </row>
     <row r="242">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>154.12</v>
+        <v>104.41</v>
       </c>
     </row>
     <row r="243">
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>108.6</v>
+        <v>51.94</v>
       </c>
     </row>
     <row r="244">
@@ -7896,7 +7896,7 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>130.34</v>
+        <v>129.79</v>
       </c>
     </row>
     <row r="245">
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>89.68000000000001</v>
+        <v>154.31</v>
       </c>
     </row>
     <row r="246">
@@ -7956,7 +7956,7 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>174.74</v>
+        <v>134.71</v>
       </c>
     </row>
     <row r="247">
@@ -7986,7 +7986,7 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>141.45</v>
+        <v>123.23</v>
       </c>
     </row>
     <row r="248">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>165.86</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="249">
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>73.06</v>
+        <v>155.07</v>
       </c>
     </row>
     <row r="250">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>92.03</v>
+        <v>102.13</v>
       </c>
     </row>
     <row r="251">
@@ -8106,7 +8106,7 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>144.24</v>
+        <v>140.2</v>
       </c>
     </row>
     <row r="252">
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>55.25</v>
+        <v>63.01</v>
       </c>
     </row>
     <row r="253">
@@ -8166,7 +8166,7 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>126.1</v>
+        <v>92.73999999999999</v>
       </c>
     </row>
     <row r="254">
@@ -8196,7 +8196,7 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>151.84</v>
+        <v>172.13</v>
       </c>
     </row>
     <row r="255">
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>146.39</v>
+        <v>145.34</v>
       </c>
     </row>
     <row r="256">
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>175.34</v>
+        <v>126.22</v>
       </c>
     </row>
     <row r="257">
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>92.45</v>
+        <v>54.17</v>
       </c>
     </row>
     <row r="258">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>93.37</v>
+        <v>51.98</v>
       </c>
     </row>
     <row r="259">
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>70.04000000000001</v>
+        <v>129.92</v>
       </c>
     </row>
     <row r="260">
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>106.54</v>
+        <v>161.92</v>
       </c>
     </row>
     <row r="261">
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>54.71</v>
+        <v>154.51</v>
       </c>
     </row>
     <row r="262">
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>103.76</v>
+        <v>113.13</v>
       </c>
     </row>
     <row r="263">
@@ -8466,7 +8466,7 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>154.86</v>
+        <v>178.98</v>
       </c>
     </row>
     <row r="264">
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>160.01</v>
+        <v>162.71</v>
       </c>
     </row>
     <row r="265">
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>72.55</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="266">
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>135.87</v>
+        <v>80.45999999999999</v>
       </c>
     </row>
     <row r="267">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>119.4</v>
+        <v>64.02</v>
       </c>
     </row>
     <row r="268">
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>108.35</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="269">
@@ -8646,7 +8646,7 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>108.63</v>
+        <v>107.37</v>
       </c>
     </row>
     <row r="270">
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>87.15000000000001</v>
+        <v>167.32</v>
       </c>
     </row>
     <row r="271">
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>176.92</v>
+        <v>148.23</v>
       </c>
     </row>
     <row r="272">
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>125.73</v>
+        <v>166.18</v>
       </c>
     </row>
     <row r="273">
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>141.13</v>
+        <v>79.92</v>
       </c>
     </row>
     <row r="274">
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>57.61</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="275">
@@ -8826,7 +8826,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>98.98999999999999</v>
+        <v>93.93000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>166.27</v>
+        <v>117.37</v>
       </c>
     </row>
     <row r="277">
@@ -8886,7 +8886,7 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>126.99</v>
+        <v>111.37</v>
       </c>
     </row>
     <row r="278">
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>57.97</v>
+        <v>157.04</v>
       </c>
     </row>
     <row r="279">
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>101.84</v>
+        <v>69.54000000000001</v>
       </c>
     </row>
     <row r="280">
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>108.96</v>
+        <v>130.09</v>
       </c>
     </row>
     <row r="281">
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>165</v>
+        <v>49.19</v>
       </c>
     </row>
     <row r="282">
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>58.34</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="283">
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>83.97</v>
+        <v>127.01</v>
       </c>
     </row>
     <row r="284">
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>128.66</v>
+        <v>140.47</v>
       </c>
     </row>
     <row r="285">
@@ -9126,7 +9126,7 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>120.42</v>
+        <v>120.7</v>
       </c>
     </row>
     <row r="286">
@@ -9156,7 +9156,7 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>137.81</v>
+        <v>69.89</v>
       </c>
     </row>
     <row r="287">
@@ -9186,7 +9186,7 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>140.83</v>
+        <v>150.1</v>
       </c>
     </row>
     <row r="288">
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>93.12</v>
+        <v>54.42</v>
       </c>
     </row>
     <row r="289">
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>63.74</v>
+        <v>168.16</v>
       </c>
     </row>
     <row r="290">
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>177.87</v>
+        <v>82.54000000000001</v>
       </c>
     </row>
     <row r="291">
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>170.06</v>
+        <v>130.02</v>
       </c>
     </row>
     <row r="292">
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>153.46</v>
+        <v>55.88</v>
       </c>
     </row>
     <row r="293">
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>163.68</v>
+        <v>84.75</v>
       </c>
     </row>
     <row r="294">
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>177.12</v>
+        <v>163.28</v>
       </c>
     </row>
     <row r="295">
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>171.97</v>
+        <v>73.98999999999999</v>
       </c>
     </row>
     <row r="296">
@@ -9456,7 +9456,7 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>55.55</v>
+        <v>123.03</v>
       </c>
     </row>
     <row r="297">
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="F297" t="n">
-        <v>110.82</v>
+        <v>104.43</v>
       </c>
     </row>
     <row r="298">
@@ -9516,7 +9516,7 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>166.77</v>
+        <v>120.13</v>
       </c>
     </row>
     <row r="299">
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>76.34</v>
+        <v>161.25</v>
       </c>
     </row>
     <row r="300">
@@ -9576,7 +9576,7 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>77.83</v>
+        <v>73.45999999999999</v>
       </c>
     </row>
     <row r="301">
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>118.71</v>
+        <v>137.84</v>
       </c>
     </row>
   </sheetData>
@@ -9700,7 +9700,7 @@
         <v>201</v>
       </c>
       <c r="H2" t="n">
-        <v>43.62</v>
+        <v>19.88</v>
       </c>
     </row>
     <row r="3">
@@ -9738,7 +9738,7 @@
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>64.19</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="4">
@@ -9776,7 +9776,7 @@
         <v>200</v>
       </c>
       <c r="H4" t="n">
-        <v>28.19</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="5">
@@ -9814,7 +9814,7 @@
         <v>200</v>
       </c>
       <c r="H5" t="n">
-        <v>29.25</v>
+        <v>73.62</v>
       </c>
     </row>
     <row r="6">
@@ -9852,7 +9852,7 @@
         <v>201</v>
       </c>
       <c r="H6" t="n">
-        <v>40.52</v>
+        <v>52.76</v>
       </c>
     </row>
     <row r="7">
@@ -9890,7 +9890,7 @@
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>65.23999999999999</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="8">
@@ -9928,7 +9928,7 @@
         <v>200</v>
       </c>
       <c r="H8" t="n">
-        <v>62.57</v>
+        <v>41.45</v>
       </c>
     </row>
     <row r="9">
@@ -9966,7 +9966,7 @@
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>67.77</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="10">
@@ -10004,7 +10004,7 @@
         <v>201</v>
       </c>
       <c r="H10" t="n">
-        <v>17.66</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="11">
@@ -10042,7 +10042,7 @@
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>26.48</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -10080,7 +10080,7 @@
         <v>200</v>
       </c>
       <c r="H12" t="n">
-        <v>76.06</v>
+        <v>75.08</v>
       </c>
     </row>
     <row r="13">
@@ -10118,7 +10118,7 @@
         <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>27.83</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="14">
@@ -10156,7 +10156,7 @@
         <v>200</v>
       </c>
       <c r="H14" t="n">
-        <v>58.96</v>
+        <v>49.19</v>
       </c>
     </row>
     <row r="15">
@@ -10194,7 +10194,7 @@
         <v>201</v>
       </c>
       <c r="H15" t="n">
-        <v>41.5</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="16">
@@ -10232,7 +10232,7 @@
         <v>200</v>
       </c>
       <c r="H16" t="n">
-        <v>48.15</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="17">
@@ -10270,7 +10270,7 @@
         <v>200</v>
       </c>
       <c r="H17" t="n">
-        <v>33.02</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="18">
@@ -10308,7 +10308,7 @@
         <v>200</v>
       </c>
       <c r="H18" t="n">
-        <v>52.46</v>
+        <v>32.27</v>
       </c>
     </row>
     <row r="19">
@@ -10346,7 +10346,7 @@
         <v>201</v>
       </c>
       <c r="H19" t="n">
-        <v>25.93</v>
+        <v>79.62</v>
       </c>
     </row>
     <row r="20">
@@ -10384,7 +10384,7 @@
         <v>200</v>
       </c>
       <c r="H20" t="n">
-        <v>76.67</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="21">
@@ -10422,7 +10422,7 @@
         <v>200</v>
       </c>
       <c r="H21" t="n">
-        <v>21.09</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="22">
@@ -10460,7 +10460,7 @@
         <v>200</v>
       </c>
       <c r="H22" t="n">
-        <v>57.54</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="23">
@@ -10498,7 +10498,7 @@
         <v>201</v>
       </c>
       <c r="H23" t="n">
-        <v>19.59</v>
+        <v>54.11</v>
       </c>
     </row>
     <row r="24">
@@ -10536,7 +10536,7 @@
         <v>200</v>
       </c>
       <c r="H24" t="n">
-        <v>82.86</v>
+        <v>26.57</v>
       </c>
     </row>
     <row r="25">
@@ -10574,7 +10574,7 @@
         <v>200</v>
       </c>
       <c r="H25" t="n">
-        <v>62.89</v>
+        <v>58.81</v>
       </c>
     </row>
     <row r="26">
@@ -10612,7 +10612,7 @@
         <v>200</v>
       </c>
       <c r="H26" t="n">
-        <v>72.87</v>
+        <v>69.59</v>
       </c>
     </row>
     <row r="27">
@@ -10650,7 +10650,7 @@
         <v>201</v>
       </c>
       <c r="H27" t="n">
-        <v>50.43</v>
+        <v>30.37</v>
       </c>
     </row>
     <row r="28">
@@ -10688,7 +10688,7 @@
         <v>200</v>
       </c>
       <c r="H28" t="n">
-        <v>40.5</v>
+        <v>80.52</v>
       </c>
     </row>
     <row r="29">
@@ -10726,7 +10726,7 @@
         <v>200</v>
       </c>
       <c r="H29" t="n">
-        <v>30.37</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="30">
@@ -10764,7 +10764,7 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>80.06999999999999</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="31">
@@ -10802,7 +10802,7 @@
         <v>200</v>
       </c>
       <c r="H31" t="n">
-        <v>31.15</v>
+        <v>83.34</v>
       </c>
     </row>
     <row r="32">
@@ -10840,7 +10840,7 @@
         <v>201</v>
       </c>
       <c r="H32" t="n">
-        <v>15.32</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="33">
@@ -10878,7 +10878,7 @@
         <v>200</v>
       </c>
       <c r="H33" t="n">
-        <v>79.44</v>
+        <v>83.83</v>
       </c>
     </row>
     <row r="34">
@@ -10916,7 +10916,7 @@
         <v>200</v>
       </c>
       <c r="H34" t="n">
-        <v>18.29</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="35">
@@ -10954,7 +10954,7 @@
         <v>200</v>
       </c>
       <c r="H35" t="n">
-        <v>62.95</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="36">
@@ -10992,7 +10992,7 @@
         <v>201</v>
       </c>
       <c r="H36" t="n">
-        <v>75.55</v>
+        <v>21.51</v>
       </c>
     </row>
     <row r="37">
@@ -11030,7 +11030,7 @@
         <v>200</v>
       </c>
       <c r="H37" t="n">
-        <v>67.11</v>
+        <v>80.04000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -11068,7 +11068,7 @@
         <v>200</v>
       </c>
       <c r="H38" t="n">
-        <v>37.52</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="39">
@@ -11106,7 +11106,7 @@
         <v>200</v>
       </c>
       <c r="H39" t="n">
-        <v>52.49</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="40">
@@ -11144,7 +11144,7 @@
         <v>201</v>
       </c>
       <c r="H40" t="n">
-        <v>63</v>
+        <v>54.36</v>
       </c>
     </row>
     <row r="41">
@@ -11182,7 +11182,7 @@
         <v>200</v>
       </c>
       <c r="H41" t="n">
-        <v>37.03</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -11220,7 +11220,7 @@
         <v>200</v>
       </c>
       <c r="H42" t="n">
-        <v>61.35</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="43">
@@ -11258,7 +11258,7 @@
         <v>200</v>
       </c>
       <c r="H43" t="n">
-        <v>81.01000000000001</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="44">
@@ -11296,7 +11296,7 @@
         <v>201</v>
       </c>
       <c r="H44" t="n">
-        <v>62.97</v>
+        <v>65.28</v>
       </c>
     </row>
     <row r="45">
@@ -11334,7 +11334,7 @@
         <v>200</v>
       </c>
       <c r="H45" t="n">
-        <v>27.56</v>
+        <v>71.69</v>
       </c>
     </row>
     <row r="46">
@@ -11372,7 +11372,7 @@
         <v>200</v>
       </c>
       <c r="H46" t="n">
-        <v>23.43</v>
+        <v>82.81</v>
       </c>
     </row>
     <row r="47">
@@ -11410,7 +11410,7 @@
         <v>200</v>
       </c>
       <c r="H47" t="n">
-        <v>34.68</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="48">
@@ -11448,7 +11448,7 @@
         <v>200</v>
       </c>
       <c r="H48" t="n">
-        <v>35.13</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="49">
@@ -11486,7 +11486,7 @@
         <v>201</v>
       </c>
       <c r="H49" t="n">
-        <v>72.72</v>
+        <v>36.61</v>
       </c>
     </row>
     <row r="50">
@@ -11524,7 +11524,7 @@
         <v>200</v>
       </c>
       <c r="H50" t="n">
-        <v>20.43</v>
+        <v>46.99</v>
       </c>
     </row>
     <row r="51">
@@ -11562,7 +11562,7 @@
         <v>200</v>
       </c>
       <c r="H51" t="n">
-        <v>57.11</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="52">
@@ -11600,7 +11600,7 @@
         <v>200</v>
       </c>
       <c r="H52" t="n">
-        <v>73.02</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="53">
@@ -11638,7 +11638,7 @@
         <v>201</v>
       </c>
       <c r="H53" t="n">
-        <v>48.57</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="54">
@@ -11676,7 +11676,7 @@
         <v>200</v>
       </c>
       <c r="H54" t="n">
-        <v>79.28</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -11714,7 +11714,7 @@
         <v>200</v>
       </c>
       <c r="H55" t="n">
-        <v>46.5</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="56">
@@ -11752,7 +11752,7 @@
         <v>200</v>
       </c>
       <c r="H56" t="n">
-        <v>70.09</v>
+        <v>63.67</v>
       </c>
     </row>
     <row r="57">
@@ -11790,7 +11790,7 @@
         <v>201</v>
       </c>
       <c r="H57" t="n">
-        <v>66.09</v>
+        <v>72.14</v>
       </c>
     </row>
     <row r="58">
@@ -11828,7 +11828,7 @@
         <v>200</v>
       </c>
       <c r="H58" t="n">
-        <v>50.07</v>
+        <v>60.39</v>
       </c>
     </row>
     <row r="59">
@@ -11866,7 +11866,7 @@
         <v>200</v>
       </c>
       <c r="H59" t="n">
-        <v>25.92</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="60">
@@ -11904,7 +11904,7 @@
         <v>200</v>
       </c>
       <c r="H60" t="n">
-        <v>42.49</v>
+        <v>35.63</v>
       </c>
     </row>
     <row r="61">
@@ -11942,7 +11942,7 @@
         <v>201</v>
       </c>
       <c r="H61" t="n">
-        <v>50.56</v>
+        <v>77.56999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -11980,7 +11980,7 @@
         <v>200</v>
       </c>
       <c r="H62" t="n">
-        <v>56.87</v>
+        <v>59.04</v>
       </c>
     </row>
     <row r="63">
@@ -12018,7 +12018,7 @@
         <v>200</v>
       </c>
       <c r="H63" t="n">
-        <v>79.8</v>
+        <v>69.94</v>
       </c>
     </row>
     <row r="64">
@@ -12056,7 +12056,7 @@
         <v>200</v>
       </c>
       <c r="H64" t="n">
-        <v>52.77</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="65">
@@ -12094,7 +12094,7 @@
         <v>200</v>
       </c>
       <c r="H65" t="n">
-        <v>63.7</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="66">
@@ -12132,7 +12132,7 @@
         <v>201</v>
       </c>
       <c r="H66" t="n">
-        <v>79.37</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="67">
@@ -12170,7 +12170,7 @@
         <v>200</v>
       </c>
       <c r="H67" t="n">
-        <v>51.55</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="68">
@@ -12208,7 +12208,7 @@
         <v>200</v>
       </c>
       <c r="H68" t="n">
-        <v>59.1</v>
+        <v>70.87</v>
       </c>
     </row>
     <row r="69">
@@ -12246,7 +12246,7 @@
         <v>200</v>
       </c>
       <c r="H69" t="n">
-        <v>29.93</v>
+        <v>37.23</v>
       </c>
     </row>
     <row r="70">
@@ -12284,7 +12284,7 @@
         <v>201</v>
       </c>
       <c r="H70" t="n">
-        <v>61.86</v>
+        <v>38.37</v>
       </c>
     </row>
     <row r="71">
@@ -12322,7 +12322,7 @@
         <v>200</v>
       </c>
       <c r="H71" t="n">
-        <v>71.47</v>
+        <v>63.42</v>
       </c>
     </row>
     <row r="72">
@@ -12360,7 +12360,7 @@
         <v>200</v>
       </c>
       <c r="H72" t="n">
-        <v>60.95</v>
+        <v>63.12</v>
       </c>
     </row>
     <row r="73">
@@ -12398,7 +12398,7 @@
         <v>200</v>
       </c>
       <c r="H73" t="n">
-        <v>23.84</v>
+        <v>24.89</v>
       </c>
     </row>
     <row r="74">
@@ -12436,7 +12436,7 @@
         <v>201</v>
       </c>
       <c r="H74" t="n">
-        <v>38.63</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="75">
@@ -12474,7 +12474,7 @@
         <v>200</v>
       </c>
       <c r="H75" t="n">
-        <v>76.73</v>
+        <v>48.03</v>
       </c>
     </row>
     <row r="76">
@@ -12512,7 +12512,7 @@
         <v>200</v>
       </c>
       <c r="H76" t="n">
-        <v>57.74</v>
+        <v>62.65</v>
       </c>
     </row>
     <row r="77">
@@ -12550,7 +12550,7 @@
         <v>200</v>
       </c>
       <c r="H77" t="n">
-        <v>30.25</v>
+        <v>41.45</v>
       </c>
     </row>
     <row r="78">
@@ -12588,7 +12588,7 @@
         <v>201</v>
       </c>
       <c r="H78" t="n">
-        <v>38.41</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="79">
@@ -12626,7 +12626,7 @@
         <v>200</v>
       </c>
       <c r="H79" t="n">
-        <v>71.90000000000001</v>
+        <v>71.93000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -12664,7 +12664,7 @@
         <v>200</v>
       </c>
       <c r="H80" t="n">
-        <v>45.88</v>
+        <v>61.74</v>
       </c>
     </row>
     <row r="81">
@@ -12702,7 +12702,7 @@
         <v>200</v>
       </c>
       <c r="H81" t="n">
-        <v>31.14</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="82">
@@ -12740,7 +12740,7 @@
         <v>200</v>
       </c>
       <c r="H82" t="n">
-        <v>64.92</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="83">
@@ -12778,7 +12778,7 @@
         <v>201</v>
       </c>
       <c r="H83" t="n">
-        <v>25.01</v>
+        <v>64.64</v>
       </c>
     </row>
     <row r="84">
@@ -12816,7 +12816,7 @@
         <v>200</v>
       </c>
       <c r="H84" t="n">
-        <v>50.89</v>
+        <v>65.18000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -12854,7 +12854,7 @@
         <v>200</v>
       </c>
       <c r="H85" t="n">
-        <v>31.31</v>
+        <v>76.11</v>
       </c>
     </row>
     <row r="86">
@@ -12892,7 +12892,7 @@
         <v>200</v>
       </c>
       <c r="H86" t="n">
-        <v>74.64</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="87">
@@ -12930,7 +12930,7 @@
         <v>201</v>
       </c>
       <c r="H87" t="n">
-        <v>70.86</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="88">
@@ -12968,7 +12968,7 @@
         <v>200</v>
       </c>
       <c r="H88" t="n">
-        <v>22.62</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="89">
@@ -13006,7 +13006,7 @@
         <v>200</v>
       </c>
       <c r="H89" t="n">
-        <v>80.14</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="90">
@@ -13044,7 +13044,7 @@
         <v>200</v>
       </c>
       <c r="H90" t="n">
-        <v>49.77</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="91">
@@ -13082,7 +13082,7 @@
         <v>201</v>
       </c>
       <c r="H91" t="n">
-        <v>32.52</v>
+        <v>37.73</v>
       </c>
     </row>
     <row r="92">
@@ -13120,7 +13120,7 @@
         <v>200</v>
       </c>
       <c r="H92" t="n">
-        <v>24.91</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="93">
@@ -13158,7 +13158,7 @@
         <v>200</v>
       </c>
       <c r="H93" t="n">
-        <v>70.78</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="94">
@@ -13196,7 +13196,7 @@
         <v>200</v>
       </c>
       <c r="H94" t="n">
-        <v>27.14</v>
+        <v>61.87</v>
       </c>
     </row>
     <row r="95">
@@ -13234,7 +13234,7 @@
         <v>201</v>
       </c>
       <c r="H95" t="n">
-        <v>42.92</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="96">
@@ -13272,7 +13272,7 @@
         <v>200</v>
       </c>
       <c r="H96" t="n">
-        <v>76.15000000000001</v>
+        <v>63.21</v>
       </c>
     </row>
     <row r="97">
@@ -13310,7 +13310,7 @@
         <v>200</v>
       </c>
       <c r="H97" t="n">
-        <v>37.65</v>
+        <v>68.06</v>
       </c>
     </row>
     <row r="98">
@@ -13348,7 +13348,7 @@
         <v>200</v>
       </c>
       <c r="H98" t="n">
-        <v>42.44</v>
+        <v>64.55</v>
       </c>
     </row>
     <row r="99">
@@ -13386,7 +13386,7 @@
         <v>200</v>
       </c>
       <c r="H99" t="n">
-        <v>48.83</v>
+        <v>29.71</v>
       </c>
     </row>
     <row r="100">
@@ -13424,7 +13424,7 @@
         <v>201</v>
       </c>
       <c r="H100" t="n">
-        <v>67.01000000000001</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="101">
@@ -13462,7 +13462,7 @@
         <v>200</v>
       </c>
       <c r="H101" t="n">
-        <v>82.45999999999999</v>
+        <v>42.06</v>
       </c>
     </row>
     <row r="102">
@@ -13500,7 +13500,7 @@
         <v>200</v>
       </c>
       <c r="H102" t="n">
-        <v>75.26000000000001</v>
+        <v>73.84</v>
       </c>
     </row>
     <row r="103">
@@ -13538,7 +13538,7 @@
         <v>200</v>
       </c>
       <c r="H103" t="n">
-        <v>53.42</v>
+        <v>83.13</v>
       </c>
     </row>
     <row r="104">
@@ -13576,7 +13576,7 @@
         <v>201</v>
       </c>
       <c r="H104" t="n">
-        <v>51.91</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="105">
@@ -13614,7 +13614,7 @@
         <v>200</v>
       </c>
       <c r="H105" t="n">
-        <v>25.17</v>
+        <v>46.09</v>
       </c>
     </row>
     <row r="106">
@@ -13652,7 +13652,7 @@
         <v>200</v>
       </c>
       <c r="H106" t="n">
-        <v>81.54000000000001</v>
+        <v>50.17</v>
       </c>
     </row>
     <row r="107">
@@ -13690,7 +13690,7 @@
         <v>200</v>
       </c>
       <c r="H107" t="n">
-        <v>34.56</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="108">
@@ -13728,7 +13728,7 @@
         <v>201</v>
       </c>
       <c r="H108" t="n">
-        <v>53.8</v>
+        <v>81.95999999999999</v>
       </c>
     </row>
     <row r="109">
@@ -13766,7 +13766,7 @@
         <v>200</v>
       </c>
       <c r="H109" t="n">
-        <v>38.21</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="110">
@@ -13804,7 +13804,7 @@
         <v>200</v>
       </c>
       <c r="H110" t="n">
-        <v>71.72</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="111">
@@ -13842,7 +13842,7 @@
         <v>200</v>
       </c>
       <c r="H111" t="n">
-        <v>78.11</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="112">
@@ -13880,7 +13880,7 @@
         <v>201</v>
       </c>
       <c r="H112" t="n">
-        <v>78.02</v>
+        <v>65.19</v>
       </c>
     </row>
     <row r="113">
@@ -13918,7 +13918,7 @@
         <v>200</v>
       </c>
       <c r="H113" t="n">
-        <v>41.68</v>
+        <v>23.22</v>
       </c>
     </row>
     <row r="114">
@@ -13956,7 +13956,7 @@
         <v>200</v>
       </c>
       <c r="H114" t="n">
-        <v>41.98</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="115">
@@ -13994,7 +13994,7 @@
         <v>200</v>
       </c>
       <c r="H115" t="n">
-        <v>78.73999999999999</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="116">
@@ -14032,7 +14032,7 @@
         <v>200</v>
       </c>
       <c r="H116" t="n">
-        <v>44.13</v>
+        <v>36.64</v>
       </c>
     </row>
     <row r="117">
@@ -14070,7 +14070,7 @@
         <v>201</v>
       </c>
       <c r="H117" t="n">
-        <v>16.44</v>
+        <v>63.38</v>
       </c>
     </row>
     <row r="118">
@@ -14108,7 +14108,7 @@
         <v>200</v>
       </c>
       <c r="H118" t="n">
-        <v>20.76</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="119">
@@ -14146,7 +14146,7 @@
         <v>200</v>
       </c>
       <c r="H119" t="n">
-        <v>22.78</v>
+        <v>72.18000000000001</v>
       </c>
     </row>
     <row r="120">
@@ -14184,7 +14184,7 @@
         <v>200</v>
       </c>
       <c r="H120" t="n">
-        <v>21.85</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="121">
@@ -14222,7 +14222,7 @@
         <v>201</v>
       </c>
       <c r="H121" t="n">
-        <v>37.67</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="122">
@@ -14260,7 +14260,7 @@
         <v>200</v>
       </c>
       <c r="H122" t="n">
-        <v>50.04</v>
+        <v>82.97</v>
       </c>
     </row>
     <row r="123">
@@ -14298,7 +14298,7 @@
         <v>200</v>
       </c>
       <c r="H123" t="n">
-        <v>71.01000000000001</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="124">
@@ -14336,7 +14336,7 @@
         <v>200</v>
       </c>
       <c r="H124" t="n">
-        <v>23.16</v>
+        <v>77.36</v>
       </c>
     </row>
     <row r="125">
@@ -14374,7 +14374,7 @@
         <v>201</v>
       </c>
       <c r="H125" t="n">
-        <v>44.31</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="126">
@@ -14412,7 +14412,7 @@
         <v>200</v>
       </c>
       <c r="H126" t="n">
-        <v>79.81</v>
+        <v>68.19</v>
       </c>
     </row>
     <row r="127">
@@ -14450,7 +14450,7 @@
         <v>200</v>
       </c>
       <c r="H127" t="n">
-        <v>52.57</v>
+        <v>82.23</v>
       </c>
     </row>
     <row r="128">
@@ -14488,7 +14488,7 @@
         <v>200</v>
       </c>
       <c r="H128" t="n">
-        <v>32.85</v>
+        <v>23.71</v>
       </c>
     </row>
     <row r="129">
@@ -14526,7 +14526,7 @@
         <v>201</v>
       </c>
       <c r="H129" t="n">
-        <v>73.75</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="130">
@@ -14564,7 +14564,7 @@
         <v>200</v>
       </c>
       <c r="H130" t="n">
-        <v>18.9</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="131">
@@ -14602,7 +14602,7 @@
         <v>200</v>
       </c>
       <c r="H131" t="n">
-        <v>30.6</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="132">
@@ -14640,7 +14640,7 @@
         <v>200</v>
       </c>
       <c r="H132" t="n">
-        <v>78.95</v>
+        <v>56.96</v>
       </c>
     </row>
     <row r="133">
@@ -14678,7 +14678,7 @@
         <v>200</v>
       </c>
       <c r="H133" t="n">
-        <v>57.77</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="134">
@@ -14716,7 +14716,7 @@
         <v>201</v>
       </c>
       <c r="H134" t="n">
-        <v>80.98</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="135">
@@ -14754,7 +14754,7 @@
         <v>200</v>
       </c>
       <c r="H135" t="n">
-        <v>30.67</v>
+        <v>43.18</v>
       </c>
     </row>
     <row r="136">
@@ -14792,7 +14792,7 @@
         <v>200</v>
       </c>
       <c r="H136" t="n">
-        <v>32.41</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="137">
@@ -14830,7 +14830,7 @@
         <v>200</v>
       </c>
       <c r="H137" t="n">
-        <v>30.23</v>
+        <v>52.53</v>
       </c>
     </row>
     <row r="138">
@@ -14868,7 +14868,7 @@
         <v>201</v>
       </c>
       <c r="H138" t="n">
-        <v>50.76</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="139">
@@ -14906,7 +14906,7 @@
         <v>200</v>
       </c>
       <c r="H139" t="n">
-        <v>74.84</v>
+        <v>64.38</v>
       </c>
     </row>
     <row r="140">
@@ -14944,7 +14944,7 @@
         <v>200</v>
       </c>
       <c r="H140" t="n">
-        <v>62.5</v>
+        <v>83.02</v>
       </c>
     </row>
     <row r="141">
@@ -14982,7 +14982,7 @@
         <v>200</v>
       </c>
       <c r="H141" t="n">
-        <v>41.98</v>
+        <v>77.58</v>
       </c>
     </row>
     <row r="142">
@@ -15020,7 +15020,7 @@
         <v>201</v>
       </c>
       <c r="H142" t="n">
-        <v>53.16</v>
+        <v>27.87</v>
       </c>
     </row>
     <row r="143">
@@ -15058,7 +15058,7 @@
         <v>200</v>
       </c>
       <c r="H143" t="n">
-        <v>20.62</v>
+        <v>59.17</v>
       </c>
     </row>
     <row r="144">
@@ -15096,7 +15096,7 @@
         <v>200</v>
       </c>
       <c r="H144" t="n">
-        <v>68.18000000000001</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="145">
@@ -15134,7 +15134,7 @@
         <v>200</v>
       </c>
       <c r="H145" t="n">
-        <v>71.75</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="146">
@@ -15172,7 +15172,7 @@
         <v>201</v>
       </c>
       <c r="H146" t="n">
-        <v>34.57</v>
+        <v>81.51000000000001</v>
       </c>
     </row>
     <row r="147">
@@ -15210,7 +15210,7 @@
         <v>200</v>
       </c>
       <c r="H147" t="n">
-        <v>28.51</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="148">
@@ -15248,7 +15248,7 @@
         <v>200</v>
       </c>
       <c r="H148" t="n">
-        <v>27.82</v>
+        <v>76.14</v>
       </c>
     </row>
     <row r="149">
@@ -15286,7 +15286,7 @@
         <v>200</v>
       </c>
       <c r="H149" t="n">
-        <v>80.26000000000001</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="150">
@@ -15324,7 +15324,7 @@
         <v>200</v>
       </c>
       <c r="H150" t="n">
-        <v>56.22</v>
+        <v>84.33</v>
       </c>
     </row>
     <row r="151">
@@ -15362,7 +15362,7 @@
         <v>201</v>
       </c>
       <c r="H151" t="n">
-        <v>29.74</v>
+        <v>40.86</v>
       </c>
     </row>
     <row r="152">
@@ -15400,7 +15400,7 @@
         <v>200</v>
       </c>
       <c r="H152" t="n">
-        <v>59.88</v>
+        <v>31.54</v>
       </c>
     </row>
     <row r="153">
@@ -15438,7 +15438,7 @@
         <v>200</v>
       </c>
       <c r="H153" t="n">
-        <v>71.52</v>
+        <v>55.79</v>
       </c>
     </row>
     <row r="154">
@@ -15476,7 +15476,7 @@
         <v>200</v>
       </c>
       <c r="H154" t="n">
-        <v>22.13</v>
+        <v>66.18000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -15514,7 +15514,7 @@
         <v>201</v>
       </c>
       <c r="H155" t="n">
-        <v>45.22</v>
+        <v>55.31</v>
       </c>
     </row>
     <row r="156">
@@ -15552,7 +15552,7 @@
         <v>200</v>
       </c>
       <c r="H156" t="n">
-        <v>77.33</v>
+        <v>75.61</v>
       </c>
     </row>
     <row r="157">
@@ -15590,7 +15590,7 @@
         <v>200</v>
       </c>
       <c r="H157" t="n">
-        <v>65.65000000000001</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="158">
@@ -15628,7 +15628,7 @@
         <v>200</v>
       </c>
       <c r="H158" t="n">
-        <v>84.84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="159">
@@ -15666,7 +15666,7 @@
         <v>201</v>
       </c>
       <c r="H159" t="n">
-        <v>52.42</v>
+        <v>69.83</v>
       </c>
     </row>
     <row r="160">
@@ -15704,7 +15704,7 @@
         <v>200</v>
       </c>
       <c r="H160" t="n">
-        <v>48.2</v>
+        <v>54.56</v>
       </c>
     </row>
     <row r="161">
@@ -15742,7 +15742,7 @@
         <v>200</v>
       </c>
       <c r="H161" t="n">
-        <v>74.59999999999999</v>
+        <v>36.09</v>
       </c>
     </row>
     <row r="162">
@@ -15780,7 +15780,7 @@
         <v>200</v>
       </c>
       <c r="H162" t="n">
-        <v>66.17</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="163">
@@ -15818,7 +15818,7 @@
         <v>201</v>
       </c>
       <c r="H163" t="n">
-        <v>66.14</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="164">
@@ -15856,7 +15856,7 @@
         <v>200</v>
       </c>
       <c r="H164" t="n">
-        <v>53.64</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="165">
@@ -15894,7 +15894,7 @@
         <v>200</v>
       </c>
       <c r="H165" t="n">
-        <v>16.27</v>
+        <v>59.72</v>
       </c>
     </row>
     <row r="166">
@@ -15932,7 +15932,7 @@
         <v>200</v>
       </c>
       <c r="H166" t="n">
-        <v>47.13</v>
+        <v>38.23</v>
       </c>
     </row>
     <row r="167">
@@ -15970,7 +15970,7 @@
         <v>200</v>
       </c>
       <c r="H167" t="n">
-        <v>31.07</v>
+        <v>34.02</v>
       </c>
     </row>
     <row r="168">
@@ -16008,7 +16008,7 @@
         <v>201</v>
       </c>
       <c r="H168" t="n">
-        <v>69.04000000000001</v>
+        <v>33.04</v>
       </c>
     </row>
     <row r="169">
@@ -16046,7 +16046,7 @@
         <v>200</v>
       </c>
       <c r="H169" t="n">
-        <v>21.57</v>
+        <v>58.32</v>
       </c>
     </row>
     <row r="170">
@@ -16084,7 +16084,7 @@
         <v>200</v>
       </c>
       <c r="H170" t="n">
-        <v>46.67</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="171">
@@ -16122,7 +16122,7 @@
         <v>200</v>
       </c>
       <c r="H171" t="n">
-        <v>76.67</v>
+        <v>56.94</v>
       </c>
     </row>
     <row r="172">
@@ -16160,7 +16160,7 @@
         <v>201</v>
       </c>
       <c r="H172" t="n">
-        <v>72.2</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="173">
@@ -16198,7 +16198,7 @@
         <v>200</v>
       </c>
       <c r="H173" t="n">
-        <v>57.94</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="174">
@@ -16236,7 +16236,7 @@
         <v>200</v>
       </c>
       <c r="H174" t="n">
-        <v>82.92</v>
+        <v>23.95</v>
       </c>
     </row>
     <row r="175">
@@ -16274,7 +16274,7 @@
         <v>200</v>
       </c>
       <c r="H175" t="n">
-        <v>46.65</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="176">
@@ -16312,7 +16312,7 @@
         <v>201</v>
       </c>
       <c r="H176" t="n">
-        <v>82.04000000000001</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="177">
@@ -16350,7 +16350,7 @@
         <v>200</v>
       </c>
       <c r="H177" t="n">
-        <v>47.19</v>
+        <v>24.47</v>
       </c>
     </row>
     <row r="178">
@@ -16388,7 +16388,7 @@
         <v>200</v>
       </c>
       <c r="H178" t="n">
-        <v>16.86</v>
+        <v>50.11</v>
       </c>
     </row>
     <row r="179">
@@ -16426,7 +16426,7 @@
         <v>200</v>
       </c>
       <c r="H179" t="n">
-        <v>52.52</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="180">
@@ -16464,7 +16464,7 @@
         <v>201</v>
       </c>
       <c r="H180" t="n">
-        <v>25.52</v>
+        <v>62.03</v>
       </c>
     </row>
     <row r="181">
@@ -16502,7 +16502,7 @@
         <v>200</v>
       </c>
       <c r="H181" t="n">
-        <v>68.5</v>
+        <v>69.29000000000001</v>
       </c>
     </row>
     <row r="182">
@@ -16540,7 +16540,7 @@
         <v>200</v>
       </c>
       <c r="H182" t="n">
-        <v>24.27</v>
+        <v>30.13</v>
       </c>
     </row>
     <row r="183">
@@ -16578,7 +16578,7 @@
         <v>200</v>
       </c>
       <c r="H183" t="n">
-        <v>26.21</v>
+        <v>78.36</v>
       </c>
     </row>
     <row r="184">
@@ -16616,7 +16616,7 @@
         <v>200</v>
       </c>
       <c r="H184" t="n">
-        <v>21.01</v>
+        <v>33.47</v>
       </c>
     </row>
     <row r="185">
@@ -16654,7 +16654,7 @@
         <v>201</v>
       </c>
       <c r="H185" t="n">
-        <v>43.25</v>
+        <v>36.77</v>
       </c>
     </row>
     <row r="186">
@@ -16692,7 +16692,7 @@
         <v>200</v>
       </c>
       <c r="H186" t="n">
-        <v>51.7</v>
+        <v>75.69</v>
       </c>
     </row>
     <row r="187">
@@ -16730,7 +16730,7 @@
         <v>200</v>
       </c>
       <c r="H187" t="n">
-        <v>17.82</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="188">
@@ -16768,7 +16768,7 @@
         <v>200</v>
       </c>
       <c r="H188" t="n">
-        <v>65.03</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="189">
@@ -16806,7 +16806,7 @@
         <v>201</v>
       </c>
       <c r="H189" t="n">
-        <v>44.86</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="190">
@@ -16844,7 +16844,7 @@
         <v>200</v>
       </c>
       <c r="H190" t="n">
-        <v>72</v>
+        <v>32.93</v>
       </c>
     </row>
     <row r="191">
@@ -16882,7 +16882,7 @@
         <v>200</v>
       </c>
       <c r="H191" t="n">
-        <v>26.23</v>
+        <v>83.56999999999999</v>
       </c>
     </row>
     <row r="192">
@@ -16920,7 +16920,7 @@
         <v>200</v>
       </c>
       <c r="H192" t="n">
-        <v>66.09999999999999</v>
+        <v>79.97</v>
       </c>
     </row>
     <row r="193">
@@ -16958,7 +16958,7 @@
         <v>201</v>
       </c>
       <c r="H193" t="n">
-        <v>74.59999999999999</v>
+        <v>70.27</v>
       </c>
     </row>
     <row r="194">
@@ -16996,7 +16996,7 @@
         <v>200</v>
       </c>
       <c r="H194" t="n">
-        <v>72.95</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="195">
@@ -17034,7 +17034,7 @@
         <v>200</v>
       </c>
       <c r="H195" t="n">
-        <v>17.77</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="196">
@@ -17072,7 +17072,7 @@
         <v>200</v>
       </c>
       <c r="H196" t="n">
-        <v>68.54000000000001</v>
+        <v>68.69</v>
       </c>
     </row>
     <row r="197">
@@ -17110,7 +17110,7 @@
         <v>201</v>
       </c>
       <c r="H197" t="n">
-        <v>42.1</v>
+        <v>81.05</v>
       </c>
     </row>
     <row r="198">
@@ -17148,7 +17148,7 @@
         <v>200</v>
       </c>
       <c r="H198" t="n">
-        <v>64.43000000000001</v>
+        <v>75.37</v>
       </c>
     </row>
     <row r="199">
@@ -17186,7 +17186,7 @@
         <v>200</v>
       </c>
       <c r="H199" t="n">
-        <v>29.91</v>
+        <v>76.34</v>
       </c>
     </row>
     <row r="200">
@@ -17224,7 +17224,7 @@
         <v>200</v>
       </c>
       <c r="H200" t="n">
-        <v>51.16</v>
+        <v>30.17</v>
       </c>
     </row>
     <row r="201">
@@ -17262,7 +17262,7 @@
         <v>200</v>
       </c>
       <c r="H201" t="n">
-        <v>30.15</v>
+        <v>75.78</v>
       </c>
     </row>
     <row r="202">
@@ -17300,7 +17300,7 @@
         <v>201</v>
       </c>
       <c r="H202" t="n">
-        <v>76.40000000000001</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="203">
@@ -17338,7 +17338,7 @@
         <v>200</v>
       </c>
       <c r="H203" t="n">
-        <v>35.41</v>
+        <v>60.86</v>
       </c>
     </row>
     <row r="204">
@@ -17376,7 +17376,7 @@
         <v>200</v>
       </c>
       <c r="H204" t="n">
-        <v>30.18</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="205">
@@ -17414,7 +17414,7 @@
         <v>200</v>
       </c>
       <c r="H205" t="n">
-        <v>48.51</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="206">
@@ -17452,7 +17452,7 @@
         <v>201</v>
       </c>
       <c r="H206" t="n">
-        <v>48.08</v>
+        <v>54.67</v>
       </c>
     </row>
     <row r="207">
@@ -17490,7 +17490,7 @@
         <v>200</v>
       </c>
       <c r="H207" t="n">
-        <v>48.97</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="208">
@@ -17528,7 +17528,7 @@
         <v>200</v>
       </c>
       <c r="H208" t="n">
-        <v>67.40000000000001</v>
+        <v>42.37</v>
       </c>
     </row>
     <row r="209">
@@ -17566,7 +17566,7 @@
         <v>200</v>
       </c>
       <c r="H209" t="n">
-        <v>17.11</v>
+        <v>50.36</v>
       </c>
     </row>
     <row r="210">
@@ -17604,7 +17604,7 @@
         <v>201</v>
       </c>
       <c r="H210" t="n">
-        <v>54.82</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="211">
@@ -17642,7 +17642,7 @@
         <v>200</v>
       </c>
       <c r="H211" t="n">
-        <v>31.51</v>
+        <v>79.87</v>
       </c>
     </row>
     <row r="212">
@@ -17680,7 +17680,7 @@
         <v>200</v>
       </c>
       <c r="H212" t="n">
-        <v>49.97</v>
+        <v>62.72</v>
       </c>
     </row>
     <row r="213">
@@ -17718,7 +17718,7 @@
         <v>200</v>
       </c>
       <c r="H213" t="n">
-        <v>41.35</v>
+        <v>71.39</v>
       </c>
     </row>
     <row r="214">
@@ -17756,7 +17756,7 @@
         <v>201</v>
       </c>
       <c r="H214" t="n">
-        <v>77.40000000000001</v>
+        <v>67.51000000000001</v>
       </c>
     </row>
     <row r="215">
@@ -17794,7 +17794,7 @@
         <v>200</v>
       </c>
       <c r="H215" t="n">
-        <v>69.67</v>
+        <v>73.84</v>
       </c>
     </row>
     <row r="216">
@@ -17832,7 +17832,7 @@
         <v>200</v>
       </c>
       <c r="H216" t="n">
-        <v>45.08</v>
+        <v>62.26</v>
       </c>
     </row>
     <row r="217">
@@ -17870,7 +17870,7 @@
         <v>200</v>
       </c>
       <c r="H217" t="n">
-        <v>32.54</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="218">
@@ -17908,7 +17908,7 @@
         <v>200</v>
       </c>
       <c r="H218" t="n">
-        <v>71.33</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="219">
@@ -17946,7 +17946,7 @@
         <v>201</v>
       </c>
       <c r="H219" t="n">
-        <v>77.14</v>
+        <v>79.20999999999999</v>
       </c>
     </row>
     <row r="220">
@@ -17984,7 +17984,7 @@
         <v>200</v>
       </c>
       <c r="H220" t="n">
-        <v>54.07</v>
+        <v>83.75</v>
       </c>
     </row>
     <row r="221">
@@ -18022,7 +18022,7 @@
         <v>200</v>
       </c>
       <c r="H221" t="n">
-        <v>15.31</v>
+        <v>29.23</v>
       </c>
     </row>
     <row r="222">
@@ -18060,7 +18060,7 @@
         <v>200</v>
       </c>
       <c r="H222" t="n">
-        <v>52.81</v>
+        <v>80.63</v>
       </c>
     </row>
     <row r="223">
@@ -18098,7 +18098,7 @@
         <v>201</v>
       </c>
       <c r="H223" t="n">
-        <v>24.54</v>
+        <v>51.15</v>
       </c>
     </row>
     <row r="224">
@@ -18136,7 +18136,7 @@
         <v>200</v>
       </c>
       <c r="H224" t="n">
-        <v>17.09</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="225">
@@ -18174,7 +18174,7 @@
         <v>200</v>
       </c>
       <c r="H225" t="n">
-        <v>81.69</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="226">
@@ -18212,7 +18212,7 @@
         <v>200</v>
       </c>
       <c r="H226" t="n">
-        <v>15.12</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="227">
@@ -18250,7 +18250,7 @@
         <v>201</v>
       </c>
       <c r="H227" t="n">
-        <v>68.95999999999999</v>
+        <v>66.87</v>
       </c>
     </row>
     <row r="228">
@@ -18288,7 +18288,7 @@
         <v>200</v>
       </c>
       <c r="H228" t="n">
-        <v>37.54</v>
+        <v>65.36</v>
       </c>
     </row>
     <row r="229">
@@ -18326,7 +18326,7 @@
         <v>200</v>
       </c>
       <c r="H229" t="n">
-        <v>17.64</v>
+        <v>33.65</v>
       </c>
     </row>
     <row r="230">
@@ -18364,7 +18364,7 @@
         <v>200</v>
       </c>
       <c r="H230" t="n">
-        <v>58.07</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="231">
@@ -18402,7 +18402,7 @@
         <v>201</v>
       </c>
       <c r="H231" t="n">
-        <v>76.15000000000001</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="232">
@@ -18440,7 +18440,7 @@
         <v>200</v>
       </c>
       <c r="H232" t="n">
-        <v>49.84</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="233">
@@ -18478,7 +18478,7 @@
         <v>200</v>
       </c>
       <c r="H233" t="n">
-        <v>33.78</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="234">
@@ -18516,7 +18516,7 @@
         <v>200</v>
       </c>
       <c r="H234" t="n">
-        <v>55.65</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="235">
@@ -18554,7 +18554,7 @@
         <v>200</v>
       </c>
       <c r="H235" t="n">
-        <v>42.65</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="236">
@@ -18592,7 +18592,7 @@
         <v>201</v>
       </c>
       <c r="H236" t="n">
-        <v>17.64</v>
+        <v>63.72</v>
       </c>
     </row>
     <row r="237">
@@ -18630,7 +18630,7 @@
         <v>200</v>
       </c>
       <c r="H237" t="n">
-        <v>74.65000000000001</v>
+        <v>65.36</v>
       </c>
     </row>
     <row r="238">
@@ -18668,7 +18668,7 @@
         <v>200</v>
       </c>
       <c r="H238" t="n">
-        <v>46.72</v>
+        <v>82.86</v>
       </c>
     </row>
     <row r="239">
@@ -18706,7 +18706,7 @@
         <v>200</v>
       </c>
       <c r="H239" t="n">
-        <v>44.83</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="240">
@@ -18744,7 +18744,7 @@
         <v>201</v>
       </c>
       <c r="H240" t="n">
-        <v>66.86</v>
+        <v>42.87</v>
       </c>
     </row>
     <row r="241">
@@ -18782,7 +18782,7 @@
         <v>200</v>
       </c>
       <c r="H241" t="n">
-        <v>58.95</v>
+        <v>78.47</v>
       </c>
     </row>
     <row r="242">
@@ -18820,7 +18820,7 @@
         <v>200</v>
       </c>
       <c r="H242" t="n">
-        <v>62.92</v>
+        <v>72.06</v>
       </c>
     </row>
     <row r="243">
@@ -18858,7 +18858,7 @@
         <v>200</v>
       </c>
       <c r="H243" t="n">
-        <v>75.65000000000001</v>
+        <v>79.06999999999999</v>
       </c>
     </row>
     <row r="244">
@@ -18896,7 +18896,7 @@
         <v>201</v>
       </c>
       <c r="H244" t="n">
-        <v>31.19</v>
+        <v>72.81</v>
       </c>
     </row>
     <row r="245">
@@ -18934,7 +18934,7 @@
         <v>200</v>
       </c>
       <c r="H245" t="n">
-        <v>39.45</v>
+        <v>43.67</v>
       </c>
     </row>
     <row r="246">
@@ -18972,7 +18972,7 @@
         <v>200</v>
       </c>
       <c r="H246" t="n">
-        <v>62.18</v>
+        <v>80.92</v>
       </c>
     </row>
     <row r="247">
@@ -19010,7 +19010,7 @@
         <v>200</v>
       </c>
       <c r="H247" t="n">
-        <v>35.57</v>
+        <v>80.81999999999999</v>
       </c>
     </row>
     <row r="248">
@@ -19048,7 +19048,7 @@
         <v>201</v>
       </c>
       <c r="H248" t="n">
-        <v>37.9</v>
+        <v>73.73999999999999</v>
       </c>
     </row>
     <row r="249">
@@ -19086,7 +19086,7 @@
         <v>200</v>
       </c>
       <c r="H249" t="n">
-        <v>15.51</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="250">
@@ -19124,7 +19124,7 @@
         <v>200</v>
       </c>
       <c r="H250" t="n">
-        <v>20.43</v>
+        <v>45.25</v>
       </c>
     </row>
     <row r="251">
@@ -19162,7 +19162,7 @@
         <v>200</v>
       </c>
       <c r="H251" t="n">
-        <v>58.53</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="252">
@@ -19200,7 +19200,7 @@
         <v>200</v>
       </c>
       <c r="H252" t="n">
-        <v>60.22</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="253">
@@ -19238,7 +19238,7 @@
         <v>201</v>
       </c>
       <c r="H253" t="n">
-        <v>48.04</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="254">
@@ -19276,7 +19276,7 @@
         <v>200</v>
       </c>
       <c r="H254" t="n">
-        <v>51.96</v>
+        <v>58.48</v>
       </c>
     </row>
     <row r="255">
@@ -19314,7 +19314,7 @@
         <v>200</v>
       </c>
       <c r="H255" t="n">
-        <v>61.05</v>
+        <v>59.91</v>
       </c>
     </row>
     <row r="256">
@@ -19352,7 +19352,7 @@
         <v>200</v>
       </c>
       <c r="H256" t="n">
-        <v>41.46</v>
+        <v>83.12</v>
       </c>
     </row>
     <row r="257">
@@ -19390,7 +19390,7 @@
         <v>201</v>
       </c>
       <c r="H257" t="n">
-        <v>58.62</v>
+        <v>60.51</v>
       </c>
     </row>
     <row r="258">
@@ -19428,7 +19428,7 @@
         <v>200</v>
       </c>
       <c r="H258" t="n">
-        <v>51.14</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -19466,7 +19466,7 @@
         <v>200</v>
       </c>
       <c r="H259" t="n">
-        <v>32.34</v>
+        <v>82</v>
       </c>
     </row>
     <row r="260">
@@ -19504,7 +19504,7 @@
         <v>200</v>
       </c>
       <c r="H260" t="n">
-        <v>43.99</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="261">
@@ -19542,7 +19542,7 @@
         <v>201</v>
       </c>
       <c r="H261" t="n">
-        <v>71.44</v>
+        <v>71.06</v>
       </c>
     </row>
     <row r="262">
@@ -19580,7 +19580,7 @@
         <v>200</v>
       </c>
       <c r="H262" t="n">
-        <v>42.95</v>
+        <v>83.86</v>
       </c>
     </row>
     <row r="263">
@@ -19618,7 +19618,7 @@
         <v>200</v>
       </c>
       <c r="H263" t="n">
-        <v>30.44</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="264">
@@ -19656,7 +19656,7 @@
         <v>200</v>
       </c>
       <c r="H264" t="n">
-        <v>70.39</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="265">
@@ -19694,7 +19694,7 @@
         <v>201</v>
       </c>
       <c r="H265" t="n">
-        <v>28.66</v>
+        <v>42.61</v>
       </c>
     </row>
     <row r="266">
@@ -19732,7 +19732,7 @@
         <v>200</v>
       </c>
       <c r="H266" t="n">
-        <v>79.39</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="267">
@@ -19770,7 +19770,7 @@
         <v>200</v>
       </c>
       <c r="H267" t="n">
-        <v>68.34999999999999</v>
+        <v>74.62</v>
       </c>
     </row>
     <row r="268">
@@ -19808,7 +19808,7 @@
         <v>200</v>
       </c>
       <c r="H268" t="n">
-        <v>35.2</v>
+        <v>75.23</v>
       </c>
     </row>
     <row r="269">
@@ -19846,7 +19846,7 @@
         <v>200</v>
       </c>
       <c r="H269" t="n">
-        <v>82.31999999999999</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="270">
@@ -19884,7 +19884,7 @@
         <v>201</v>
       </c>
       <c r="H270" t="n">
-        <v>28.19</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="271">
@@ -19922,7 +19922,7 @@
         <v>200</v>
       </c>
       <c r="H271" t="n">
-        <v>55.99</v>
+        <v>77.84999999999999</v>
       </c>
     </row>
     <row r="272">
@@ -19960,7 +19960,7 @@
         <v>200</v>
       </c>
       <c r="H272" t="n">
-        <v>60.86</v>
+        <v>74.41</v>
       </c>
     </row>
     <row r="273">
@@ -19998,7 +19998,7 @@
         <v>200</v>
       </c>
       <c r="H273" t="n">
-        <v>18.55</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="274">
@@ -20036,7 +20036,7 @@
         <v>201</v>
       </c>
       <c r="H274" t="n">
-        <v>31.37</v>
+        <v>37.54</v>
       </c>
     </row>
     <row r="275">
@@ -20074,7 +20074,7 @@
         <v>200</v>
       </c>
       <c r="H275" t="n">
-        <v>70.97</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="276">
@@ -20112,7 +20112,7 @@
         <v>200</v>
       </c>
       <c r="H276" t="n">
-        <v>21.84</v>
+        <v>64.75</v>
       </c>
     </row>
     <row r="277">
@@ -20150,7 +20150,7 @@
         <v>200</v>
       </c>
       <c r="H277" t="n">
-        <v>23.24</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="278">
@@ -20188,7 +20188,7 @@
         <v>201</v>
       </c>
       <c r="H278" t="n">
-        <v>41.53</v>
+        <v>71.37</v>
       </c>
     </row>
     <row r="279">
@@ -20226,7 +20226,7 @@
         <v>200</v>
       </c>
       <c r="H279" t="n">
-        <v>38.27</v>
+        <v>31.89</v>
       </c>
     </row>
     <row r="280">
@@ -20264,7 +20264,7 @@
         <v>200</v>
       </c>
       <c r="H280" t="n">
-        <v>83.23999999999999</v>
+        <v>29.14</v>
       </c>
     </row>
     <row r="281">
@@ -20302,7 +20302,7 @@
         <v>200</v>
       </c>
       <c r="H281" t="n">
-        <v>71.12</v>
+        <v>70.95</v>
       </c>
     </row>
     <row r="282">
@@ -20340,7 +20340,7 @@
         <v>201</v>
       </c>
       <c r="H282" t="n">
-        <v>53.15</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="283">
@@ -20378,7 +20378,7 @@
         <v>200</v>
       </c>
       <c r="H283" t="n">
-        <v>43.08</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="284">
@@ -20416,7 +20416,7 @@
         <v>200</v>
       </c>
       <c r="H284" t="n">
-        <v>38.2</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="285">
@@ -20454,7 +20454,7 @@
         <v>200</v>
       </c>
       <c r="H285" t="n">
-        <v>38.87</v>
+        <v>31.86</v>
       </c>
     </row>
     <row r="286">
@@ -20492,7 +20492,7 @@
         <v>200</v>
       </c>
       <c r="H286" t="n">
-        <v>16.69</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="287">
@@ -20530,7 +20530,7 @@
         <v>201</v>
       </c>
       <c r="H287" t="n">
-        <v>55.36</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="288">
@@ -20568,7 +20568,7 @@
         <v>200</v>
       </c>
       <c r="H288" t="n">
-        <v>18.96</v>
+        <v>32.52</v>
       </c>
     </row>
     <row r="289">
@@ -20606,7 +20606,7 @@
         <v>200</v>
       </c>
       <c r="H289" t="n">
-        <v>74.72</v>
+        <v>60.06</v>
       </c>
     </row>
     <row r="290">
@@ -20644,7 +20644,7 @@
         <v>200</v>
       </c>
       <c r="H290" t="n">
-        <v>65.73999999999999</v>
+        <v>82.31</v>
       </c>
     </row>
     <row r="291">
@@ -20682,7 +20682,7 @@
         <v>201</v>
       </c>
       <c r="H291" t="n">
-        <v>55.93</v>
+        <v>72.43000000000001</v>
       </c>
     </row>
     <row r="292">
@@ -20720,7 +20720,7 @@
         <v>200</v>
       </c>
       <c r="H292" t="n">
-        <v>65.84999999999999</v>
+        <v>25.83</v>
       </c>
     </row>
     <row r="293">
@@ -20758,7 +20758,7 @@
         <v>200</v>
       </c>
       <c r="H293" t="n">
-        <v>55.91</v>
+        <v>36.66</v>
       </c>
     </row>
     <row r="294">
@@ -20796,7 +20796,7 @@
         <v>200</v>
       </c>
       <c r="H294" t="n">
-        <v>68.86</v>
+        <v>25.87</v>
       </c>
     </row>
     <row r="295">
@@ -20834,7 +20834,7 @@
         <v>201</v>
       </c>
       <c r="H295" t="n">
-        <v>40.39</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="296">
@@ -20872,7 +20872,7 @@
         <v>200</v>
       </c>
       <c r="H296" t="n">
-        <v>17.07</v>
+        <v>56.13</v>
       </c>
     </row>
     <row r="297">
@@ -20910,7 +20910,7 @@
         <v>200</v>
       </c>
       <c r="H297" t="n">
-        <v>55.96</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="298">
@@ -20948,7 +20948,7 @@
         <v>200</v>
       </c>
       <c r="H298" t="n">
-        <v>43.15</v>
+        <v>75.95</v>
       </c>
     </row>
     <row r="299">
@@ -20986,7 +20986,7 @@
         <v>201</v>
       </c>
       <c r="H299" t="n">
-        <v>83.45</v>
+        <v>67.81999999999999</v>
       </c>
     </row>
     <row r="300">
@@ -21024,7 +21024,7 @@
         <v>200</v>
       </c>
       <c r="H300" t="n">
-        <v>82.47</v>
+        <v>18.85</v>
       </c>
     </row>
     <row r="301">
@@ -21062,7 +21062,7 @@
         <v>200</v>
       </c>
       <c r="H301" t="n">
-        <v>71.76000000000001</v>
+        <v>75.11</v>
       </c>
     </row>
   </sheetData>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.9</t>
         </is>
       </c>
     </row>
@@ -21159,7 +21159,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87.03</t>
+          <t>84.06</t>
         </is>
       </c>
     </row>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>139.78</t>
+          <t>139.37</t>
         </is>
       </c>
     </row>
@@ -21195,7 +21195,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>84.92</t>
+          <t>82.59</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>130.43</t>
+          <t>128.92</t>
         </is>
       </c>
     </row>
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>139.37</t>
+          <t>138.67</t>
         </is>
       </c>
     </row>
